--- a/outputs/evaluation/architecture/design/v2/CF_M08/run_2/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v2/CF_M08/run_2/CF_M08_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.4516</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.6087</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.4483</v>
       </c>
       <c r="D3" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9777</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.5</v>
       </c>
       <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8375</v>
       </c>
     </row>
@@ -1221,14 +1235,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Observer</t>
@@ -1247,14 +1258,11 @@
       <c r="P2" t="n">
         <v>66</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M08_P04</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1275,7 +1283,6 @@
       <c r="D3" t="n">
         <v>0.8375</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1296,7 +1303,6 @@
           <t>['AU_03', 'AU_06']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_11</t>
@@ -1307,7 +1313,6 @@
           <t>system service, data service</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1326,7 +1331,6 @@
           <t>CF_M08_AU04, CF_M08_AU08</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M08_AU24</t>
@@ -1377,14 +1381,11 @@
           <t>67</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Singleton</t>
@@ -1403,14 +1404,11 @@
       <c r="P4" t="n">
         <v>67</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M08_P05</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1451,14 +1449,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Component-based</t>
@@ -1477,14 +1472,11 @@
       <c r="P5" t="n">
         <v>66</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M08_P03</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1525,14 +1517,11 @@
           <t>41, 43</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Security Service</t>
@@ -1556,13 +1545,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1608,13 +1595,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>React</t>
@@ -1638,13 +1623,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M08_AU06</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1685,14 +1668,11 @@
           <t>41, 42</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Data Service</t>
@@ -1716,13 +1696,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1763,14 +1741,11 @@
           <t>41, 42, 76</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Docker</t>
@@ -1794,13 +1769,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M08_AU22</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1846,13 +1819,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
@@ -1876,13 +1847,11 @@
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M08_AU08</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1923,14 +1892,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -1949,14 +1915,11 @@
       <c r="P11" t="n">
         <v>41</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2002,13 +1965,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Traefik</t>
@@ -2032,13 +1993,11 @@
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M08_AU03</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2079,14 +2038,11 @@
           <t>41, 42</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>System Service</t>
@@ -2110,13 +2066,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2162,13 +2116,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Next.js</t>
@@ -2192,13 +2144,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M08_AU05</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2244,13 +2194,11 @@
           <t>['AU_03', 'AU_06']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Prisma</t>
@@ -2274,13 +2222,11 @@
           <t>CF_M08_P02</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M08_AU09</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2349,7 +2295,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>security service, system service</t>
@@ -2446,7 +2391,6 @@
           <t>Amazon EC2</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>These services run on Amazon EC2 instances</t>
@@ -2477,7 +2421,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
@@ -2518,7 +2461,6 @@
           <t>Authentication</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Authentication: Use Google for user authentication.</t>
@@ -2554,7 +2496,6 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Authentication: Use Google for user authentication.</t>
@@ -2590,7 +2531,6 @@
           <t>Cloud storage</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Cloud storage: Use Amazon S3 to store and retrieve files.</t>
@@ -2626,7 +2566,6 @@
           <t>Amazon S3</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Cloud storage: Use Amazon S3 to store and retrieve files.</t>
@@ -2662,7 +2601,6 @@
           <t>Payment processing</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Payment processing: Integrates with Stripe to manage payments and subscriptions tions.</t>
@@ -2698,7 +2636,6 @@
           <t>Stripe</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Payment processing: Integrates with Stripe to manage payments and subscriptions tions.</t>
@@ -2734,7 +2671,6 @@
           <t>Analytics</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Analytics: Implement Google Analytics to track and analyze the traffic of the site.</t>
@@ -2770,7 +2706,6 @@
           <t>Google Analytics</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Implement Google Analytics to track and analyze site traffic</t>
@@ -2806,7 +2741,6 @@
           <t>Error monitoring</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Error monitoring: Use Sentry to track and manage errors in the application.</t>
@@ -2842,7 +2776,6 @@
           <t>Sentry</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Error monitoring: Use Sentry to track and manage errors in the application.</t>
@@ -2878,7 +2811,6 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Connects to Brevo to create, send and schedule emails electronics.</t>
@@ -2914,7 +2846,6 @@
           <t>Brevo</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Connects to Brevo to create, send and schedule emails.</t>
@@ -2950,7 +2881,6 @@
           <t>HTTPS</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>HTTPS, which is the standard for secure communications on the web</t>
@@ -2961,7 +2891,6 @@
           <t>AU_10</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>0.7334000000000001</v>
       </c>
@@ -2982,7 +2911,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
@@ -2993,7 +2921,6 @@
           <t>AU_11</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>0.6632</v>
       </c>
@@ -3014,7 +2941,6 @@
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
